--- a/data/trans_dic/P16A13-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A13-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,3</t>
+          <t>0,57; 2,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,11; 6,51</t>
+          <t>3,04; 6,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,49</t>
+          <t>2,4; 5,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,76; 12,92</t>
+          <t>7,66; 12,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,4</t>
+          <t>1,9; 4,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,15; 6,51</t>
+          <t>3,29; 6,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,23; 6,51</t>
+          <t>3,28; 6,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,0; 14,1</t>
+          <t>10,93; 14,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,91</t>
+          <t>1,4; 2,82</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,48; 5,9</t>
+          <t>3,46; 5,84</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,29; 5,4</t>
+          <t>3,22; 5,41</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,96; 12,96</t>
+          <t>9,83; 12,83</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,57</t>
+          <t>2,14; 4,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,72; 5,34</t>
+          <t>2,8; 5,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,85; 4,04</t>
+          <t>1,95; 4,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,12; 5,63</t>
+          <t>1,77; 5,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,05; 4,34</t>
+          <t>2,09; 4,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,92; 6,92</t>
+          <t>3,88; 7,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 4,83</t>
+          <t>2,43; 4,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,61; 10,21</t>
+          <t>7,65; 10,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,45; 4,02</t>
+          <t>2,38; 4,03</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,66; 5,52</t>
+          <t>3,63; 5,56</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 3,98</t>
+          <t>2,42; 4,09</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,16; 7,38</t>
+          <t>4,23; 7,42</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,47; 5,39</t>
+          <t>2,34; 5,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,41; 5,18</t>
+          <t>2,46; 5,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,5</t>
+          <t>1,86; 4,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,61; 6,53</t>
+          <t>3,67; 6,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,2; 6,36</t>
+          <t>3,28; 6,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,49; 6,57</t>
+          <t>3,33; 6,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,64; 5,74</t>
+          <t>2,69; 5,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 5,81</t>
+          <t>1,94; 5,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,19; 5,28</t>
+          <t>3,15; 5,26</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,34; 5,46</t>
+          <t>3,27; 5,49</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,61; 4,59</t>
+          <t>2,57; 4,63</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,88; 5,63</t>
+          <t>2,87; 5,56</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,64</t>
+          <t>1,59; 3,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,09; 6,29</t>
+          <t>3,06; 6,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 3,96</t>
+          <t>1,63; 3,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,34; 8,37</t>
+          <t>5,36; 8,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,83; 5,29</t>
+          <t>2,78; 5,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,81; 7,93</t>
+          <t>4,88; 8,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,11; 5,94</t>
+          <t>3,09; 5,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,62; 8,56</t>
+          <t>5,8; 8,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,0</t>
+          <t>2,47; 4,02</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,45; 6,68</t>
+          <t>4,38; 6,44</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,67; 4,38</t>
+          <t>2,69; 4,46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,99; 8,07</t>
+          <t>6,0; 8,09</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,16; 3,32</t>
+          <t>2,15; 3,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,34; 4,87</t>
+          <t>3,43; 4,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,39; 3,61</t>
+          <t>2,36; 3,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,74; 6,97</t>
+          <t>4,55; 6,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,02; 4,21</t>
+          <t>3,01; 4,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,62; 6,23</t>
+          <t>4,59; 6,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,38; 4,83</t>
+          <t>3,44; 4,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,32; 8,69</t>
+          <t>6,44; 8,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,69; 3,53</t>
+          <t>2,72; 3,57</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,24; 5,31</t>
+          <t>4,26; 5,29</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,08; 3,98</t>
+          <t>3,05; 4,0</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,05; 7,63</t>
+          <t>6,02; 7,58</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3924; 15959</t>
+          <t>3922; 14847</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>21694; 45398</t>
+          <t>21176; 46202</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16095; 37075</t>
+          <t>16210; 35803</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49307; 82084</t>
+          <t>48696; 82210</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13238; 30264</t>
+          <t>13081; 31585</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21837; 45218</t>
+          <t>22870; 46218</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21725; 43777</t>
+          <t>22100; 44469</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>74364; 95256</t>
+          <t>73858; 96621</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19165; 40189</t>
+          <t>19295; 39022</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>48455; 82041</t>
+          <t>48220; 81312</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44300; 72833</t>
+          <t>43379; 72877</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>130615; 169908</t>
+          <t>128946; 168166</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21362; 43989</t>
+          <t>20576; 43017</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27684; 54387</t>
+          <t>28459; 53464</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18872; 41310</t>
+          <t>19917; 41973</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25254; 67213</t>
+          <t>21137; 65850</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19838; 42026</t>
+          <t>20278; 41874</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40269; 71117</t>
+          <t>39849; 72536</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24710; 50348</t>
+          <t>25373; 50707</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>72912; 97866</t>
+          <t>73252; 97932</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>47203; 77673</t>
+          <t>45949; 77715</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>74857; 112844</t>
+          <t>74202; 113808</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49022; 82104</t>
+          <t>49894; 84539</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>89429; 158823</t>
+          <t>91041; 159575</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16771; 36593</t>
+          <t>15850; 35952</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18266; 39204</t>
+          <t>18627; 40923</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13359; 34197</t>
+          <t>14111; 34306</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25378; 45961</t>
+          <t>25840; 47430</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>21911; 43488</t>
+          <t>22412; 43229</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27109; 50979</t>
+          <t>25812; 51609</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20744; 45091</t>
+          <t>21154; 45396</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20686; 54170</t>
+          <t>18110; 53754</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>43416; 71890</t>
+          <t>42969; 71666</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51189; 83627</t>
+          <t>50165; 84089</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>40388; 70891</t>
+          <t>39744; 71516</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>47118; 92190</t>
+          <t>46920; 90963</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14777; 34287</t>
+          <t>14949; 34599</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29165; 59401</t>
+          <t>28903; 59997</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15727; 37132</t>
+          <t>15268; 35177</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>49534; 77556</t>
+          <t>49649; 75546</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29355; 54907</t>
+          <t>28915; 53767</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>50454; 83194</t>
+          <t>51181; 84581</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32452; 61973</t>
+          <t>32214; 59579</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>61300; 93474</t>
+          <t>63264; 93790</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>47880; 79214</t>
+          <t>48964; 79698</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>88744; 133185</t>
+          <t>87284; 128340</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>52954; 86711</t>
+          <t>53374; 88460</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>120845; 162822</t>
+          <t>120992; 163212</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>70617; 108614</t>
+          <t>70576; 106821</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>114170; 166447</t>
+          <t>117282; 167490</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>81052; 122688</t>
+          <t>80122; 121868</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>164059; 241010</t>
+          <t>157256; 239591</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>101921; 142388</t>
+          <t>101559; 142806</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>163853; 220822</t>
+          <t>162886; 219087</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>119777; 171144</t>
+          <t>121848; 171702</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>231207; 317937</t>
+          <t>235759; 319722</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>178837; 234861</t>
+          <t>181139; 237608</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>295469; 369878</t>
+          <t>296390; 368209</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>213981; 276229</t>
+          <t>211384; 277284</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>430868; 543050</t>
+          <t>428459; 539202</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A13-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A13-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,55%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,14</t>
+          <t>0,56; 2,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,04; 6,62</t>
+          <t>3,16; 6,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,31</t>
+          <t>2,35; 5,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,66; 12,94</t>
+          <t>7,1; 11,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,59</t>
+          <t>1,92; 4,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,29; 6,66</t>
+          <t>3,17; 6,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,28; 6,61</t>
+          <t>3,27; 6,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,93; 14,3</t>
+          <t>10,64; 14,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,82</t>
+          <t>1,39; 2,86</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,46; 5,84</t>
+          <t>3,49; 5,88</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,22; 5,41</t>
+          <t>3,23; 5,45</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,83; 12,83</t>
+          <t>9,36; 12,07</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 4,47</t>
+          <t>2,14; 4,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,8; 5,25</t>
+          <t>2,7; 5,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,11</t>
+          <t>1,93; 4,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 5,52</t>
+          <t>3,91; 6,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,09; 4,32</t>
+          <t>2,16; 4,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,88; 7,06</t>
+          <t>3,93; 6,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,43; 4,86</t>
+          <t>2,39; 4,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,65; 10,22</t>
+          <t>7,25; 10,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,38; 4,03</t>
+          <t>2,37; 4,03</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,63; 5,56</t>
+          <t>3,64; 5,58</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,09</t>
+          <t>2,4; 4,05</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,23; 7,42</t>
+          <t>6,03; 7,9</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,34; 5,3</t>
+          <t>2,33; 5,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,41</t>
+          <t>2,54; 5,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,52</t>
+          <t>1,79; 4,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,67; 6,74</t>
+          <t>3,57; 6,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,28; 6,32</t>
+          <t>3,21; 6,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,33; 6,65</t>
+          <t>3,41; 6,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,69; 5,78</t>
+          <t>2,8; 5,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,94; 5,76</t>
+          <t>4,2; 6,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,15; 5,26</t>
+          <t>3,17; 5,24</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,27; 5,49</t>
+          <t>3,3; 5,39</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 4,63</t>
+          <t>2,58; 4,68</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,87; 5,56</t>
+          <t>4,29; 6,34</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,67</t>
+          <t>1,6; 3,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,06; 6,36</t>
+          <t>3,17; 6,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,75</t>
+          <t>1,61; 3,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,36; 8,15</t>
+          <t>5,38; 8,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,78; 5,18</t>
+          <t>2,86; 5,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,88; 8,06</t>
+          <t>4,88; 7,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,09; 5,71</t>
+          <t>3,13; 5,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,8; 8,59</t>
+          <t>6,64; 9,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,47; 4,02</t>
+          <t>2,47; 4,11</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,38; 6,44</t>
+          <t>4,32; 6,61</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,69; 4,46</t>
+          <t>2,68; 4,52</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,0; 8,09</t>
+          <t>6,41; 8,32</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 3,26</t>
+          <t>2,14; 3,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,43; 4,9</t>
+          <t>3,4; 4,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,36; 3,59</t>
+          <t>2,42; 3,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,55; 6,93</t>
+          <t>5,49; 7,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,01; 4,23</t>
+          <t>3,02; 4,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,59; 6,18</t>
+          <t>4,67; 6,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,44; 4,84</t>
+          <t>3,36; 4,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,44; 8,74</t>
+          <t>7,65; 9,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,72; 3,57</t>
+          <t>2,74; 3,6</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,26; 5,29</t>
+          <t>4,23; 5,29</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,05; 4,0</t>
+          <t>3,07; 3,99</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,02; 7,58</t>
+          <t>6,79; 7,9</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62083</t>
+          <t>60944</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>84501</t>
+          <t>89295</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>146584</t>
+          <t>150239</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3922; 14847</t>
+          <t>3898; 15088</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>21176; 46202</t>
+          <t>22010; 48143</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16210; 35803</t>
+          <t>15853; 35752</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48696; 82210</t>
+          <t>49036; 77801</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13081; 31585</t>
+          <t>13231; 30342</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22870; 46218</t>
+          <t>22009; 45438</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22100; 44469</t>
+          <t>21984; 44896</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>73858; 96621</t>
+          <t>77987; 103104</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19295; 39022</t>
+          <t>19178; 39572</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>48220; 81312</t>
+          <t>48630; 81878</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43379; 72877</t>
+          <t>43536; 73417</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>128946; 168166</t>
+          <t>133209; 171848</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>48443</t>
+          <t>53330</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>84810</t>
+          <t>92908</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>133253</t>
+          <t>146238</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20576; 43017</t>
+          <t>20538; 41812</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28459; 53464</t>
+          <t>27522; 55186</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19917; 41973</t>
+          <t>19741; 41961</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21137; 65850</t>
+          <t>41000; 67213</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20278; 41874</t>
+          <t>20912; 41269</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39849; 72536</t>
+          <t>40400; 70779</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25373; 50707</t>
+          <t>24875; 49971</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>73252; 97932</t>
+          <t>77605; 107610</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>45949; 77715</t>
+          <t>45751; 77774</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>74202; 113808</t>
+          <t>74451; 114181</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49894; 84539</t>
+          <t>49655; 83620</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>91041; 159575</t>
+          <t>127908; 167423</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34644</t>
+          <t>39199</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>38310</t>
+          <t>43483</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>72954</t>
+          <t>82681</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15850; 35952</t>
+          <t>15834; 35503</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18627; 40923</t>
+          <t>19216; 39839</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14111; 34306</t>
+          <t>13595; 35573</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25840; 47430</t>
+          <t>28618; 52741</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>22412; 43229</t>
+          <t>21918; 43945</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25812; 51609</t>
+          <t>26457; 52857</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21154; 45396</t>
+          <t>21967; 45689</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18110; 53754</t>
+          <t>34119; 54420</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>42969; 71666</t>
+          <t>43255; 71420</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>50165; 84089</t>
+          <t>50615; 82586</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>39744; 71516</t>
+          <t>39906; 72255</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>46920; 90963</t>
+          <t>69155; 102247</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62956</t>
+          <t>66901</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>78890</t>
+          <t>87034</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>141845</t>
+          <t>153935</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14949; 34599</t>
+          <t>15061; 34844</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28903; 59997</t>
+          <t>29904; 57634</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15268; 35177</t>
+          <t>15097; 34670</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>49649; 75546</t>
+          <t>53303; 81809</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28915; 53767</t>
+          <t>29659; 53834</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>51181; 84581</t>
+          <t>51148; 82670</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32214; 59579</t>
+          <t>32664; 61875</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>63264; 93790</t>
+          <t>74218; 101951</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>48964; 79698</t>
+          <t>48922; 81503</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>87284; 128340</t>
+          <t>86163; 131708</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>53374; 88460</t>
+          <t>53058; 89555</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>120992; 163212</t>
+          <t>134979; 175241</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>208125</t>
+          <t>220373</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>286511</t>
+          <t>312720</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>494636</t>
+          <t>533093</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>70576; 106821</t>
+          <t>70173; 105971</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>117282; 167490</t>
+          <t>116213; 165627</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>80122; 121868</t>
+          <t>82159; 123631</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>157256; 239591</t>
+          <t>193771; 249185</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>101559; 142806</t>
+          <t>102113; 142944</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>162886; 219087</t>
+          <t>165743; 220736</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>121848; 171702</t>
+          <t>119203; 171138</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>235759; 319722</t>
+          <t>285399; 338445</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>181139; 237608</t>
+          <t>182237; 239500</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>296390; 368209</t>
+          <t>294840; 368516</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>211384; 277284</t>
+          <t>213192; 277135</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>428459; 539202</t>
+          <t>493532; 573701</t>
         </is>
       </c>
     </row>
